--- a/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
@@ -941,7 +941,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Padre Sposa</t>
@@ -950,7 +950,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Madre Sposo</t>
@@ -959,7 +959,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposo</t>
@@ -986,7 +986,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposa</t>
@@ -1007,13 +1007,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Figlio</t>
@@ -1052,7 +1052,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Atto Nascita Figlio</t>
@@ -1070,13 +1070,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Assenso figlio</t>
@@ -1103,7 +1103,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Dati Riconoscimento - Generalità discendenti - Matrimoni</t>
@@ -1256,13 +1256,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1366,7 +1366,7 @@
     <col min="4" max="4" width="68.45703125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="33.79296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="28.28125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="119.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11586,10 +11586,10 @@
         <v>307</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>308</v>
@@ -12230,10 +12230,10 @@
         <v>310</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D473" s="2" t="s">
         <v>311</v>
@@ -12874,10 +12874,10 @@
         <v>313</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D501" s="2" t="s">
         <v>314</v>
@@ -13702,10 +13702,10 @@
         <v>322</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>323</v>
@@ -14530,10 +14530,10 @@
         <v>329</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D573" s="2" t="s">
         <v>330</v>
@@ -15174,10 +15174,10 @@
         <v>332</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D601" s="2" t="s">
         <v>330</v>
@@ -17635,10 +17635,10 @@
         <v>350</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D708" s="2" t="s">
         <v>351</v>
@@ -18279,10 +18279,10 @@
         <v>353</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D736" s="2" t="s">
         <v>351</v>
@@ -20269,7 +20269,7 @@
         <v>415</v>
       </c>
       <c r="F822" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G822" s="2" t="s">
         <v>59</v>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_013.xlsx
@@ -9036,7 +9036,7 @@
         <v>233</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>270</v>
